--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/ImagingStudy</t>
+    <t>http://hl7.org/fhir/StructureDefinition/ImagingStudy|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -373,7 +373,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -561,7 +561,7 @@
     <t>内視鏡を表すモダリティコード”ES”を指定する。複数モダリティを使用した場合には、該当するモダリティコードを並記する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS|1.3.0-dev</t>
   </si>
   <si>
     <t>.code</t>
@@ -576,7 +576,7 @@
     <t>ImagingStudy.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -604,7 +604,7 @@
     <t>ImagingStudy.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -661,7 +661,7 @@
     <t>ImagingStudy.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ServiceRequest|Appointment|AppointmentResponse|Task)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1|Appointment|4.0.1|AppointmentResponse|4.0.1|Task|4.0.1)
 </t>
   </si>
   <si>
@@ -696,7 +696,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -743,7 +743,7 @@
     <t>ImagingStudy.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -807,7 +807,7 @@
     <t>ImagingStudy.procedureReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -858,7 +858,7 @@
     <t>ImagingStudy.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -904,7 +904,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ReasonCodesJed_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ReasonCodesJed_VS|1.1.0</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -922,7 +922,7 @@
     <t>ImagingStudy.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Endoscopy)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Endoscopy|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1178,7 +1178,7 @@
     <t>このシリーズの対象となる解剖学的部位。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ImagingStudy_Radiology_BodySite_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ImagingStudy_Radiology_BodySite_VS|1.3.0-dev</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -1199,7 +1199,7 @@
     <t>適用される部位の側性を示すコード（左側、右側など）</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/bodysite-laterality</t>
+    <t>http://hl7.org/fhir/ValueSet/bodysite-laterality|4.0.1</t>
   </si>
   <si>
     <t>(0020,0060)</t>
@@ -1208,7 +1208,7 @@
     <t>ImagingStudy.series.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1288,13 +1288,13 @@
     <t>パフォーマーの関与のタイプ</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/series-performer-function</t>
+    <t>http://hl7.org/fhir/ValueSet/series-performer-function|4.0.1</t>
   </si>
   <si>
     <t>ImagingStudy.series.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|Device|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|Device|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1377,7 +1377,7 @@
 　Secondary Capture Image Storage:1.2.840.10008.5.1.4.1.1.7</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/imaging-service-request-ig/ValueSet/dicom-sop-classes</t>
+    <t>http://hl7.org/fhir/uv/imaging-service-request-ig/ValueSet/dicom-sop-classes|0.1.0</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP]. source[classCode=OBS, moodCode=EVN, code="sop class"].value</t>
@@ -1755,7 +1755,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="75.44140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="107.140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1770,7 +1770,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="24.4765625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.0" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.2265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/ImagingStudy|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/ImagingStudy</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -373,7 +373,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -561,7 +561,7 @@
     <t>内視鏡を表すモダリティコード”ES”を指定する。複数モダリティを使用した場合には、該当するモダリティコードを並記する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DICOMModality_VS</t>
   </si>
   <si>
     <t>.code</t>
@@ -576,7 +576,7 @@
     <t>ImagingStudy.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
 </t>
   </si>
   <si>
@@ -604,7 +604,7 @@
     <t>ImagingStudy.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
 </t>
   </si>
   <si>
@@ -661,7 +661,7 @@
     <t>ImagingStudy.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1|Appointment|4.0.1|AppointmentResponse|4.0.1|Task|4.0.1)
+    <t xml:space="preserve">Reference(CarePlan|ServiceRequest|Appointment|AppointmentResponse|Task)
 </t>
   </si>
   <si>
@@ -696,7 +696,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner)
 </t>
   </si>
   <si>
@@ -743,7 +743,7 @@
     <t>ImagingStudy.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint|4.0.1)
+    <t xml:space="preserve">Reference(Endpoint)
 </t>
   </si>
   <si>
@@ -807,7 +807,7 @@
     <t>ImagingStudy.procedureReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure)
 </t>
   </si>
   <si>
@@ -858,7 +858,7 @@
     <t>ImagingStudy.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Location)
 </t>
   </si>
   <si>
@@ -904,7 +904,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ReasonCodesJed_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ReasonCodesJed_VS</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -922,7 +922,7 @@
     <t>ImagingStudy.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Endoscopy|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Endoscopy)
 </t>
   </si>
   <si>
@@ -1178,7 +1178,7 @@
     <t>このシリーズの対象となる解剖学的部位。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ImagingStudy_Radiology_BodySite_VS|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ImagingStudy_Radiology_BodySite_VS</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -1199,7 +1199,7 @@
     <t>適用される部位の側性を示すコード（左側、右側など）</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/bodysite-laterality|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/bodysite-laterality</t>
   </si>
   <si>
     <t>(0020,0060)</t>
@@ -1208,7 +1208,7 @@
     <t>ImagingStudy.series.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1)
+    <t xml:space="preserve">Reference(Specimen)
 </t>
   </si>
   <si>
@@ -1288,13 +1288,13 @@
     <t>パフォーマーの関与のタイプ</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/series-performer-function|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/series-performer-function</t>
   </si>
   <si>
     <t>ImagingStudy.series.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|Device|4.0.1|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|Device|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1377,7 +1377,7 @@
 　Secondary Capture Image Storage:1.2.840.10008.5.1.4.1.1.7</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/imaging-service-request-ig/ValueSet/dicom-sop-classes|0.1.0</t>
+    <t>http://hl7.org/fhir/uv/imaging-service-request-ig/ValueSet/dicom-sop-classes</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP]. source[classCode=OBS, moodCode=EVN, code="sop class"].value</t>
@@ -1755,7 +1755,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="107.140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="75.44140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1770,7 +1770,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="24.4765625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.2265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.0" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
